--- a/data-collection/generated/generated-qa-200.xlsx
+++ b/data-collection/generated/generated-qa-200.xlsx
@@ -526,7 +526,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Domestic undergraduate students apply through the state admissions centre (the state Tertiary Admissions Centre). The the state admissions centre code for the Bachelor of Information Technology is 733001. Interstate students also apply through the state admissions centre.</t>
+          <t>Domestic undergraduate students apply through the state admissions centre (the state Tertiary Admissions Centre). The state admissions centre code for the Bachelor of Information Technology is 733001. Interstate students also apply through the state admissions centre.</t>
         </is>
       </c>
     </row>
@@ -598,7 +598,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>For Chinese students, successful completion of the first year of a bachelor's degree at a Chinese university is typically the the state Year 12 equivalent accepted by the University. You should contact the University International Admissions at anon@example.edu to confirm your specific eligibility.</t>
+          <t>For Chinese students, successful completion of the first year of a bachelor's degree at a Chinese university is typically the state Year 12 equivalent accepted by the University. You should contact the University International Admissions at anon@example.edu to confirm your specific eligibility.</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Singapore-Cambridge GCE A Levels are accepted as the the state Year 12 equivalent. For English proficiency, you need a grade of C or better in the General Paper or Knowledge and Inquiry subject, or grade C in H2 English Language and Linguistics or Literature in English. You also need to satisfy the mathematics prerequisite and meet the minimum entry score.</t>
+          <t>Singapore-Cambridge GCE A Levels are accepted as the state Year 12 equivalent. For English proficiency, you need a grade of C or better in the General Paper or Knowledge and Inquiry subject, or grade C in H2 English Language and Linguistics or Literature in English. You also need to satisfy the mathematics prerequisite and meet the minimum entry score.</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>The Bachelor of Information Technology is a 3-year full-time program, or part-time equivalent. It is offered at the the main campus campus with intakes in Semester 1 (23 February 2026) and Semester 2 (27 July 2026).</t>
+          <t>The Bachelor of Information Technology is a 3-year full-time program, or part-time equivalent. It is offered at the main campus with intakes in Semester 1 (23 February 2026) and Semester 2 (27 July 2026).</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Yes. The BIT is available for both Semester 1 (commencing 23 February 2026) and Semester 2 (commencing 27 July 2026) intakes at the the main campus campus.</t>
+          <t>Yes. The BIT is available for both Semester 1 (commencing 23 February 2026) and Semester 2 (commencing 27 July 2026) intakes at the main campus.</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>The Bachelors of Information Technology / Arts is a 4-year full-time program, available for both Semester 1 and Semester 2 intakes at the the main campus campus.</t>
+          <t>The Bachelors of Information Technology / Arts is a 4-year full-time program, available for both Semester 1 and Semester 2 intakes at the main campus.</t>
         </is>
       </c>
     </row>
@@ -826,7 +826,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>The Bachelors of Business Management / Information Technology is a 4-year full-time program, with intakes in both Semester 1 and Semester 2 at the the main campus campus.</t>
+          <t>The Bachelors of Business Management / Information Technology is a 4-year full-time program, with intakes in both Semester 1 and Semester 2 at the main campus.</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>The BIT and all its dual degree combinations are delivered at the the main campus campus, the University's main campus located 7km from the city's city centre.</t>
+          <t>The BIT and all its dual degree combinations are delivered at the main campus, the University's main campus located 7km from the city's city centre.</t>
         </is>
       </c>
     </row>
@@ -1030,7 +1030,7 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>The the University International Guide 2026 lists Computer Systems as a minor option in the BIT program. A minor is a smaller specialisation within your degree. Check Programs and Courses for the specific course requirements and whether this minor is available in your commencement year.</t>
+          <t>The University International Guide 2026 lists Computer Systems as a minor option in the BIT program. A minor is a smaller specialisation within your degree. Check Programs and Courses for the specific course requirements and whether this minor is available in your commencement year.</t>
         </is>
       </c>
     </row>
@@ -1349,72 +1349,72 @@
     <row r="76" ht="30" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>What is the the state admissions centre code for the Bachelors of Engineering (Honours) / Information Technology?</t>
+          <t>What is the state admissions centre code for the Bachelors of Engineering (Honours) / Information Technology?</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>The the state admissions centre code for the Bachelors of Engineering (Honours) / Information Technology is 717701.</t>
+          <t>The state admissions centre code for the Bachelors of Engineering (Honours) / Information Technology is 717701.</t>
         </is>
       </c>
     </row>
     <row r="77" ht="30" customHeight="1">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>What is the the state admissions centre code for the Bachelors of Business Management / Information Technology?</t>
+          <t>What is the state admissions centre code for the Bachelors of Business Management / Information Technology?</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>The the state admissions centre code for the Bachelors of Business Management / Information Technology is 710401.</t>
+          <t>The state admissions centre code for the Bachelors of Business Management / Information Technology is 710401.</t>
         </is>
       </c>
     </row>
     <row r="78" ht="30" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>What is the the state admissions centre code for the Bachelors of Commerce / Information Technology?</t>
+          <t>What is the state admissions centre code for the Bachelors of Commerce / Information Technology?</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>The the state admissions centre code for the Bachelors of Commerce / Information Technology is 711621.</t>
+          <t>The state admissions centre code for the Bachelors of Commerce / Information Technology is 711621.</t>
         </is>
       </c>
     </row>
     <row r="79" ht="30" customHeight="1">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>What is the the state admissions centre code for the Bachelors of Information Technology / Arts?</t>
+          <t>What is the state admissions centre code for the Bachelors of Information Technology / Arts?</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>The the state admissions centre code for the Bachelors of Information Technology / Arts is 733201.</t>
+          <t>The state admissions centre code for the Bachelors of Information Technology / Arts is 733201.</t>
         </is>
       </c>
     </row>
     <row r="80" ht="30" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>What is the the state admissions centre code for the Bachelors of Information Technology / Design?</t>
+          <t>What is the state admissions centre code for the Bachelors of Information Technology / Design?</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>The the state admissions centre code for the Bachelors of Information Technology / Design is 733310.</t>
+          <t>The state admissions centre code for the Bachelors of Information Technology / Design is 733310.</t>
         </is>
       </c>
     </row>
     <row r="81" ht="30" customHeight="1">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>What is the the state admissions centre code for the Bachelors of Human Movement and Nutrition Sciences / Information Technology?</t>
+          <t>What is the state admissions centre code for the Bachelors of Human Movement and Nutrition Sciences / Information Technology?</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>The the state admissions centre code for the Bachelors of Human Movement and Nutrition Sciences / Information Technology is 720802.</t>
+          <t>The state admissions centre code for the Bachelors of Human Movement and Nutrition Sciences / Information Technology is 720802.</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Yes. The Bachelors of Human Movement and Nutrition Sciences / Information Technology is available for both Semester 1 (23 February 2026) and Semester 2 (27 July 2026) at the the main campus campus.</t>
+          <t>Yes. The Bachelors of Human Movement and Nutrition Sciences / Information Technology is available for both Semester 1 (23 February 2026) and Semester 2 (27 July 2026) at the main campus.</t>
         </is>
       </c>
     </row>
@@ -1841,12 +1841,12 @@
     <row r="117" ht="45" customHeight="1">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>What healthcare facilities are available at the the main campus campus for BIT students?</t>
+          <t>What healthcare facilities are available at the main campus for BIT students?</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>The the main campus campus has a University Health Care clinic, the University Dental clinic, and Campus Pharmacy on campus. There is also a safety escort service, a Safety Bus running from 6pm, and the University SafeZone app connecting students to security officers or emergency services.</t>
+          <t>The main campus has a University Health Care clinic, the University Dental clinic, and Campus Pharmacy on campus. There is also a safety escort service, a Safety Bus running from 6pm, and the University SafeZone app connecting students to security officers or emergency services.</t>
         </is>
       </c>
     </row>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>Yes. the University has over 220 clubs and societies, including technology, coding, gaming, and entrepreneurship clubs relevant to IT and computing students. Explore available clubs at uqu.com.au/clubs-and-societies.</t>
+          <t>Yes. the University has over 220 clubs and societies, including technology, coding, gaming, and entrepreneurship clubs relevant to IT and computing students. Explore available clubs at the Student Union.com.au/clubs-and-societies.</t>
         </is>
       </c>
     </row>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>The the main campus campus library provides academic information resources, welcoming study spaces, a world-class collection, and knowledgeable staff to assist with research and study questions. Online resources and study rooms are also available. More information is at library.example.edu.</t>
+          <t>The main campus library provides academic information resources, welcoming study spaces, a world-class collection, and knowledgeable staff to assist with research and study questions. Online resources and study rooms are also available. More information is at library.example.edu.</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>Yes. The the University Student Union (UQU) can assist with legal or migration support. Contact uqu.com.au for details on available legal advice services for enrolled students.</t>
+          <t>Yes. The University Student Union (the Student Union) can assist with legal or migration support. Contact the Student Union.com.au for details on available legal advice services for enrolled students.</t>
         </is>
       </c>
     </row>
@@ -1978,14 +1978,14 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>The the University SafeZone app connects students directly with the University security officers or emergency services from your mobile phone. It also provides a safety escort feature if you want someone to accompany you to public transport or your car. The Safety Bus also runs around the the main campus campus from 6pm.</t>
+          <t>The University SafeZone app connects students directly with the University security officers or emergency services from your mobile phone. It also provides a safety escort feature if you want someone to accompany you to public transport or your car. The Safety Bus also runs around the main campus from 6pm.</t>
         </is>
       </c>
     </row>
     <row r="129" ht="60" customHeight="1">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>What public transport options are available for getting to the the main campus campus?</t>
+          <t>What public transport options are available for getting to the main campus?</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>Yes. The BIT (Honours) is available for both Semester 1 (23 February 2026) and Semester 2 (27 July 2026) intakes at the the main campus campus.</t>
+          <t>Yes. The BIT (Honours) is available for both Semester 1 (23 February 2026) and Semester 2 (27 July 2026) intakes at the main campus.</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>Yes. The the University BIT (Honours) program is ranked #1 in the state for computer science and information systems, according to the QS World University Rankings 2026.</t>
+          <t>Yes. The University BIT (Honours) program is ranked #1 in the state for computer science and information systems, according to the QS World University Rankings 2026.</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>Domestic students apply through the state admissions centre (the state Tertiary Admissions Centre) at qtac.edu.au. The the state admissions centre code for the Bachelor of Information Technology is 733001. Interstate students also apply through the state admissions centre.</t>
+          <t>Domestic students apply through the state admissions centre (the state Tertiary Admissions Centre) at admissions.example.edu. The state admissions centre code for the Bachelor of Information Technology is 733001. Interstate students also apply through the state admissions centre.</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>Yes. If you cannot apply online, submit in person or by mail to: Future Students and Admissions, Level 2, JD Story Building, the main campus, the University, the city, QLD 4072, Australia. You can also email anon@example.edu to request an application form.</t>
+          <t>Yes. If you cannot apply online, submit in person or by mail to: Future Students and Admissions, Level 2, the Administration Building, the main campus, the University, the city, the state 0000, Australia. You can also email anon@example.edu to request an application form.</t>
         </is>
       </c>
     </row>
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>The the University Student Union (UQU) is the student representative body offering legal and migration support, clubs and societies, events, and student advocacy. BIT students can join IT and computing clubs through UQU and access legal advice at uqu.com.au.</t>
+          <t>The University Student Union (the Student Union) is the student representative body offering legal and migration support, clubs and societies, events, and student advocacy. BIT students can join IT and computing clubs through the Student Union and access legal advice at the Student Union.com.au.</t>
         </is>
       </c>
     </row>

--- a/data-collection/generated/generated-qa-200.xlsx
+++ b/data-collection/generated/generated-qa-200.xlsx
@@ -922,7 +922,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>The CRICOS code for the Bachelor of Information Technology is 001952K. CRICOS registration confirms that a program is approved for international students on a student visa.</t>
+          <t>The CRICOS code for the Bachelor of Information Technology is CRIC001. CRICOS registration confirms that a program is approved for international students on a student visa.</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>You may be able to change your major, but you should not assume all completed courses will count towards the new major. Whether they count depends on how they fit the new major, BIT core requirements, or elective categories. Seek academic advice from the School of EECS before making the change.</t>
+          <t>You may be able to change your major, but you should not assume all completed courses will count towards the new major. Whether they count depends on how they fit the new major, BIT core requirements, or elective categories. Seek academic advice from the School of the School before making the change.</t>
         </is>
       </c>
     </row>
@@ -1109,36 +1109,36 @@
     <row r="56" ht="60" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>What is CSSE1001 and what does it cover?</t>
+          <t>What is CORE1001 and what does it cover?</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>CSSE1001 is Introduction to Software Engineering, typically the first programming course in the BIT and Computer Science programs. It introduces fundamental programming concepts using Python and foundational software engineering practices. No prior programming experience is required as a prerequisite.</t>
+          <t>CORE1001 is Introduction to Software Engineering, typically the first programming course in the BIT and Computer Science programs. It introduces fundamental programming concepts using Python and foundational software engineering practices. No prior programming experience is required as a prerequisite.</t>
         </is>
       </c>
     </row>
     <row r="57" ht="60" customHeight="1">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>What is INFS1200 and why is it important in the BIT?</t>
+          <t>What is INFO1200 and why is it important in the BIT?</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>INFS1200 is Introduction to Information Systems, a foundational first-year course covering database concepts, information management, and the role of information systems in organisations. It is a prerequisite for several later courses in the Software Information Systems major, so completing it early is important.</t>
+          <t>INFO1200 is Introduction to Information Systems, a foundational first-year course covering database concepts, information management, and the role of information systems in organisations. It is a prerequisite for several later courses in the Software Information Systems major, so completing it early is important.</t>
         </is>
       </c>
     </row>
     <row r="58" ht="45" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>What is DECO1400 and what does it focus on?</t>
+          <t>What is DSGN1400 and what does it focus on?</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>DECO1400 is Introduction to Web Design, a first-year course covering the fundamentals of web technologies, HTML, CSS, and user interface design. It is typically a foundational course for the User Experience Design major and the DECO-series courses.</t>
+          <t>DSGN1400 is Introduction to Web Design, a first-year course covering the fundamentals of web technologies, HTML, CSS, and user interface design. It is typically a foundational course for the User Experience Design major and the DECO-series courses.</t>
         </is>
       </c>
     </row>
@@ -1157,12 +1157,12 @@
     <row r="60" ht="45" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>What is DECO3801 and when should I take it?</t>
+          <t>What is DSGN3801 and when should I take it?</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>DECO3801 is a capstone project course in the DECO series, typically taken in the final year of the BIT program. It involves a substantial team project combining design and technical skills. It is a core graduation requirement for BIT students following the DECO pathway.</t>
+          <t>DSGN3801 is a capstone project course in the DECO series, typically taken in the final year of the BIT program. It involves a substantial team project combining design and technical skills. It is a core graduation requirement for BIT students following the DECO pathway.</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Overloading beyond the standard 8-unit semester load requires approval. You should contact the School of EECS or the EAIT Faculty to request permission. Overloading without approval is not permitted and the extra courses may not count towards your program requirements.</t>
+          <t>Overloading beyond the standard 8-unit semester load requires approval. You should contact the School of the School or the Faculty to request permission. Overloading without approval is not permitted and the extra courses may not count towards your program requirements.</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
     <row r="64" ht="45" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>What is CSSE2002 and is it a prerequisite for advanced BIT courses?</t>
+          <t>What is CORE2002 and is it a prerequisite for advanced BIT courses?</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>CSSE2002 is Programming in the Large, a second-year course building on CSSE1001. It covers object-oriented design, software architecture, and large-scale software development. It is typically a prerequisite for several Year 2 and Year 3 CSSE courses in the BIT program.</t>
+          <t>CORE2002 is Programming in the Large, a second-year course building on CORE1001. It covers object-oriented design, software architecture, and large-scale software development. It is typically a prerequisite for several Year 2 and Year 3 CSSE courses in the BIT program.</t>
         </is>
       </c>
     </row>
@@ -1234,19 +1234,19 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Semester 2 commencing students should follow the study plan specifically designed for their commencement semester - not the Semester 1 plan, which has a different course sequence. Use the study plan for your specific major and commencement semester available from EECS or Programs and Courses.</t>
+          <t>Semester 2 commencing students should follow the study plan specifically designed for their commencement semester - not the Semester 1 plan, which has a different course sequence. Use the study plan for your specific major and commencement semester available from the School or Programs and Courses.</t>
         </is>
       </c>
     </row>
     <row r="67" ht="45" customHeight="1">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>I passed CSSE1001 with a grade of 4 out of 7. Can I continue to second-year CSSE courses?</t>
+          <t>I passed CORE1001 with a grade of 4 out of 7. Can I continue to second-year CSSE courses?</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>A grade of 4 is a pass on the University's 7-point scale. In most cases, you can progress to second-year CSSE courses if you have passed CSSE1001 and meet other listed prerequisites. Confirm whether the next course specifies a minimum grade requirement beyond a simple pass.</t>
+          <t>A grade of 4 is a pass on the University's 7-point scale. In most cases, you can progress to second-year CSSE courses if you have passed CORE1001 and meet other listed prerequisites. Confirm whether the next course specifies a minimum grade requirement beyond a simple pass.</t>
         </is>
       </c>
     </row>
@@ -1258,19 +1258,19 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Yes. The BIT typically requires a capstone project in the final year. For students following the DECO pathway, this is usually DECO3801. The specific capstone requirement depends on your major and commencement year. Check your program requirements on Programs and Courses.</t>
+          <t>Yes. The BIT typically requires a capstone project in the final year. For students following the DECO pathway, this is usually DSGN3801. The specific capstone requirement depends on your major and commencement year. Check your program requirements on Programs and Courses.</t>
         </is>
       </c>
     </row>
     <row r="69" ht="45" customHeight="1">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>What is INFS2200 and what are its prerequisites?</t>
+          <t>What is INFO2200 and what are its prerequisites?</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>INFS2200 is Relational Database Systems, a second-year course covering database design, SQL, and relational theory. It typically has INFS1200 as a prerequisite. It is a key course for students in the Software Information Systems major.</t>
+          <t>INFO2200 is Relational Database Systems, a second-year course covering database design, SQL, and relational theory. It typically has INFO1200 as a prerequisite. It is a key course for students in the Software Information Systems major.</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Study plans - the suggested semester-by-semester course sequence - are available from the School of Electrical Engineering and Computer Science (EECS) website at eecs.example.edu and through Programs and Courses. Use the plan that matches your commencement year and semester.</t>
+          <t>Study plans - the suggested semester-by-semester course sequence - are available from the School of Computing (the School) website at cs.example.edu and through Programs and Courses. Use the plan that matches your commencement year and semester.</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>Yes. International students can apply for the BE(Hons)/IT. The English requirement is 'Minimum' IELTS 6.5. Program code is 9009, CRICOS 080731B. International tuition fees are approximately AUD $58,056 per year for 2026.</t>
+          <t>Yes. International students can apply for the BE(Hons)/IT. The English requirement is 'Minimum' IELTS 6.5. Program code is 9009, CRICOS CRIC003. International tuition fees are approximately AUD $58,056 per year for 2026.</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>A transfer may be possible, but it depends on which courses you have completed and how they satisfy the BIT program requirements. You should seek academic advice from the School of EECS or your faculty before making any change, as the process is not automatic.</t>
+          <t>A transfer may be possible, but it depends on which courses you have completed and how they satisfy the BIT program requirements. You should seek academic advice from the School of the School or your faculty before making any change, as the process is not automatic.</t>
         </is>
       </c>
     </row>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>the University offers on-campus accommodation through 10 residential colleges (including Cromwell, Duchesne, Emmanuel, Grace, International House, King's, St John's, St Leo's, The Women's College, and Union College), and Kev Carmody House, the University's newest 610-room student residence at the main campus. Off-campus options include purpose-built student accommodation and private housing supported by the University Accommodation team.</t>
+          <t>the University offers on-campus accommodation through 10 residential colleges (including a college, a college, Emmanuel, Grace, International House, King's, St John's, a college, The Women's College, and Union College), and a new student residence, the University's newest 610-room student residence at the main campus. Off-campus options include purpose-built student accommodation and private housing supported by the University Accommodation team.</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>Yes. the University's Women in Computing Program (WiC) encourages girls and women to pursue technology careers and fosters a sense of belonging for Computer Science and IT students. More information is available at eait.example.edu/wic.</t>
+          <t>Yes. the University's Women in Computing Program (WiC) encourages girls and women to pursue technology careers and fosters a sense of belonging for Computer Science and IT students. More information is available at the Faculty.example.edu/wic.</t>
         </is>
       </c>
     </row>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>the University supports work-integrated learning through enrichment programs, internships, global study, and industry events. Specific placement opportunities depend on your major and courses. Explore the University Enhance Your Employability program at study.example.edu/enhance-your-employability for available options.</t>
+          <t>the University supports work-integrated learning through enrichment programs, internships, global study, and industry events. Specific placement opportunities depend on your major and courses. Explore the University the career-development program at study.example.edu/enhance-your-employability for available options.</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>the University is ranked equal 40th globally (QS World University Rankings 2025). The BIT (Honours) program is ranked #1 in the state for computer science and information systems (QS World University Rankings 2026). the University's EECS faculty has won 12 national teaching awards in the last 10 years.</t>
+          <t>the University is ranked equal 40th globally (QS World University Rankings 2025). The BIT (Honours) program is ranked #1 in the state for computer science and information systems (QS World University Rankings 2026). the University's the School faculty has won 12 national teaching awards in the last 10 years.</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>the University provides career services through the Enhance Your Employability program, including global study, internships, career workshops, research projects, and industry events. The EAIT faculty has industry connections through research partnerships and employer networks relevant to IT careers.</t>
+          <t>the University provides career services through the career-development program, including global study, internships, career workshops, research projects, and industry events. The Faculty has industry connections through research partnerships and employer networks relevant to IT careers.</t>
         </is>
       </c>
     </row>
@@ -2518,7 +2518,7 @@
       </c>
       <c r="B173" s="3" t="inlineStr">
         <is>
-          <t>the University supports global study, internships, and volunteer opportunities through the Enhance Your Employability program. the University's 350,000 alumni across 190 countries and broad global partnerships create significant international opportunities. Enquire about specific exchange programs available to IT students at study.example.edu.</t>
+          <t>the University supports global study, internships, and volunteer opportunities through the career-development program. the University's 350,000 alumni across 190 countries and broad global partnerships create significant international opportunities. Enquire about specific exchange programs available to IT students at study.example.edu.</t>
         </is>
       </c>
     </row>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="B175" s="3" t="inlineStr">
         <is>
-          <t>You should check the current accreditation status of the BIT on the program's page at study.example.edu or by contacting the School of EECS, as accreditation status and conditions can change. ACS accreditation affects eligibility for professional ACS membership after graduation.</t>
+          <t>You should check the current accreditation status of the BIT on the program's page at study.example.edu or by contacting the School of the School, as accreditation status and conditions can change. ACS accreditation affects eligibility for professional ACS membership after graduation.</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>A transfer may be possible, depending on which courses you have completed and whether they satisfy BCS entry and credit requirements. Contact the School of EECS or the EAIT faculty for formal academic advice before attempting a transfer, as the process is not automatic.</t>
+          <t>A transfer may be possible, depending on which courses you have completed and whether they satisfy BCS entry and credit requirements. Contact the School of the School or the Faculty for formal academic advice before attempting a transfer, as the process is not automatic.</t>
         </is>
       </c>
     </row>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="B181" s="3" t="inlineStr">
         <is>
-          <t>Cyber security career pathways are listed for EECS graduates. While the BIT does not have a dedicated Cyber Security major (unlike the Bachelor of Computer Science), relevant content and electives may be available. For deeper specialisation, consider the BCS Cyber Security major or the postgraduate Master of Cyber Security (5257).</t>
+          <t>Cyber security career pathways are listed for the School graduates. While the BIT does not have a dedicated Cyber Security major (unlike the Bachelor of Computer Science), relevant content and electives may be available. For deeper specialisation, consider the BCS Cyber Security major or the postgraduate Master of Cyber Security (5257).</t>
         </is>
       </c>
     </row>
@@ -2674,7 +2674,7 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>Peer Assisted Study Sessions (PASS) are facilitated by second- and third-year students who achieved top grades in specific courses. They provide advice on course content and study habits. PASS is particularly useful for first-year BIT courses like CSSE1001 and INFS1200. Ask your faculty for details on PASS sessions for your courses.</t>
+          <t>Peer Assisted Study Sessions (PASS) are facilitated by second- and third-year students who achieved top grades in specific courses. They provide advice on course content and study habits. PASS is particularly useful for first-year BIT courses like CORE1001 and INFO1200. Ask your faculty for details on PASS sessions for your courses.</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>Both codes appear in the University documentation as the Bachelor of Information Technology. Code 9002 (CRICOS 001952K) appears in the University International Guide 2026, while 9004 appears on the study.example.edu program page for 2026 entry. These may reflect a program update. Refer to study.example.edu for the current program code and confirm with admissions if uncertain.</t>
+          <t>Both codes appear in the University documentation as the Bachelor of Information Technology. Code 9002 (CRICOS CRIC001) appears in the University International Guide 2026, while 9004 appears on the study.example.edu program page for 2026 entry. These may reflect a program update. Refer to study.example.edu for the current program code and confirm with admissions if uncertain.</t>
         </is>
       </c>
     </row>
@@ -2765,7 +2765,7 @@
     <row r="194" ht="60" customHeight="1">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>Does the University provide tutoring support for BIT courses such as CSSE1001 or DECO1400?</t>
+          <t>Does the University provide tutoring support for BIT courses such as CORE1001 or DSGN1400?</t>
         </is>
       </c>
       <c r="B194" s="2" t="inlineStr">
@@ -2801,12 +2801,12 @@
     <row r="197" ht="75" customHeight="1">
       <c r="A197" s="3" t="inlineStr">
         <is>
-          <t>What is DECO3801 and why is it important in the BIT degree?</t>
+          <t>What is DSGN3801 and why is it important in the BIT degree?</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr">
         <is>
-          <t>DECO3801 (Design &amp; Computation Studio 2 / Projects in Computing) is a capstone project course in the BIT. It requires students to work in multidisciplinary teams to design, prototype, and evaluate a computing product for a real client. It integrates skills from across the degree and is typically taken in the final year. It is a core requirement for BIT students and is not offered in Summer Semester.</t>
+          <t>DSGN3801 (Design &amp; Computation Studio 2 / Projects in Computing) is a capstone project course in the BIT. It requires students to work in multidisciplinary teams to design, prototype, and evaluate a computing product for a real client. It integrates skills from across the degree and is typically taken in the final year. It is a core requirement for BIT students and is not offered in Summer Semester.</t>
         </is>
       </c>
     </row>
@@ -2837,12 +2837,12 @@
     <row r="200" ht="60" customHeight="1">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>What are the prerequisites for INFS1200 Introduction to Information Systems?</t>
+          <t>What are the prerequisites for INFO1200 Introduction to Information Systems?</t>
         </is>
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>INFS1200 has no listed prerequisites at the University and is designed as a first-year introductory course. It covers database concepts, entity-relationship modelling, SQL, and data management. It is a required course for most BIT study plans and should ideally be completed in your first year. Completing INFS1200 is a prerequisite for INFS2200 (Relational Database Systems) in second year.</t>
+          <t>INFO1200 has no listed prerequisites at the University and is designed as a first-year introductory course. It covers database concepts, entity-relationship modelling, SQL, and data management. It is a required course for most BIT study plans and should ideally be completed in your first year. Completing INFO1200 is a prerequisite for INFO2200 (Relational Database Systems) in second year.</t>
         </is>
       </c>
     </row>

--- a/data-collection/generated/generated-qa-200.xlsx
+++ b/data-collection/generated/generated-qa-200.xlsx
@@ -1138,7 +1138,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>DSGN1400 is Introduction to Web Design, a first-year course covering the fundamentals of web technologies, HTML, CSS, and user interface design. It is typically a foundational course for the User Experience Design major and the DECO-series courses.</t>
+          <t>DSGN1400 is Introduction to Web Design, a first-year course covering the fundamentals of web technologies, HTML, CSS, and user interface design. It is typically a foundational course for the User Experience Design major and the DSGN-series courses.</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>DSGN3801 is a capstone project course in the DECO series, typically taken in the final year of the BIT program. It involves a substantial team project combining design and technical skills. It is a core graduation requirement for BIT students following the DECO pathway.</t>
+          <t>DSGN3801 is a capstone project course in the DSGN series, typically taken in the final year of the BIT program. It involves a substantial team project combining design and technical skills. It is a core graduation requirement for BIT students following the DSGN pathway.</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>CORE2002 is Programming in the Large, a second-year course building on CORE1001. It covers object-oriented design, software architecture, and large-scale software development. It is typically a prerequisite for several Year 2 and Year 3 CSSE courses in the BIT program.</t>
+          <t>CORE2002 is Programming in the Large, a second-year course building on CORE1001. It covers object-oriented design, software architecture, and large-scale software development. It is typically a prerequisite for several Year 2 and Year 3 CORE courses in the BIT program.</t>
         </is>
       </c>
     </row>
@@ -1241,12 +1241,12 @@
     <row r="67" ht="45" customHeight="1">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>I passed CORE1001 with a grade of 4 out of 7. Can I continue to second-year CSSE courses?</t>
+          <t>I passed CORE1001 with a grade of 4 out of 7. Can I continue to second-year CORE courses?</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>A grade of 4 is a pass on the University's 7-point scale. In most cases, you can progress to second-year CSSE courses if you have passed CORE1001 and meet other listed prerequisites. Confirm whether the next course specifies a minimum grade requirement beyond a simple pass.</t>
+          <t>A grade of 4 is a pass on the University's 7-point scale. In most cases, you can progress to second-year CORE courses if you have passed CORE1001 and meet other listed prerequisites. Confirm whether the next course specifies a minimum grade requirement beyond a simple pass.</t>
         </is>
       </c>
     </row>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Yes. The BIT typically requires a capstone project in the final year. For students following the DECO pathway, this is usually DSGN3801. The specific capstone requirement depends on your major and commencement year. Check your program requirements on Programs and Courses.</t>
+          <t>Yes. The BIT typically requires a capstone project in the final year. For students following the DSGN pathway, this is usually DSGN3801. The specific capstone requirement depends on your major and commencement year. Check your program requirements on Programs and Courses.</t>
         </is>
       </c>
     </row>
@@ -1289,12 +1289,12 @@
     <row r="71" ht="60" customHeight="1">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>What is the role of DECO courses in the BIT program?</t>
+          <t>What is the role of DSGN courses in the BIT program?</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>DECO (Design and Computing) courses form the design stream of the BIT. They cover web design, interaction design, team-based design projects, and human-centred computing. DECO courses are particularly central to the User Experience Design major but also appear in the core curriculum for other majors.</t>
+          <t>DSGN (Design and Computing) courses form the design stream of the BIT. They cover web design, interaction design, team-based design projects, and human-centred computing. DSGN courses are particularly central to the User Experience Design major but also appear in the core curriculum for other majors.</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
     <row r="119" ht="60" customHeight="1">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>What is the Jump Start Academic Preparation Program (JSAPP) at the University?</t>
+          <t>What is the an academic preparation program at the University?</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>JSAPP is a program held before semester starts, designed to help new students - particularly international students - transition into university academic life. It covers study skills, university systems, and academic expectations. It is held before semester starts and is available through Student Support and Wellbeing Services.</t>
+          <t>the program is a program held before semester starts, designed to help new students - particularly international students - transition into university academic life. It covers study skills, university systems, and academic expectations. It is held before semester starts and is available through Student Support and Wellbeing Services.</t>
         </is>
       </c>
     </row>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>Yes. the University has over 220 clubs and societies, including technology, coding, gaming, and entrepreneurship clubs relevant to IT and computing students. Explore available clubs at the Student Union.com.au/clubs-and-societies.</t>
+          <t>Yes. the University has over 220 clubs and societies, including technology, coding, gaming, and entrepreneurship clubs relevant to IT and computing students. Explore available clubs at studentunion.example.edu/clubs-and-societies.</t>
         </is>
       </c>
     </row>
@@ -1918,7 +1918,7 @@
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>the University offers a free English for Academic Communication (EAC) program through the University College, delivered as workshops during semester. Academic English support covers a range of skills and topics. Contact Student Support and Wellbeing Services or check uqcollege.edu.au for available options.</t>
+          <t>the University offers a free an academic English program through the University College, delivered as workshops during semester. Academic English support covers a range of skills and topics. Contact Student Support and Wellbeing Services or check unicollege.edu.au for available options.</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>Yes. the University's Women in Computing Program (WiC) encourages girls and women to pursue technology careers and fosters a sense of belonging for Computer Science and IT students. More information is available at the Faculty.example.edu/wic.</t>
+          <t>Yes. the University's Women in Computing Program (WiC) encourages girls and women to pursue technology careers and fosters a sense of belonging for Computer Science and IT students. More information is available at dept.example.edu/wic.</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>Yes. The University Student Union (the Student Union) can assist with legal or migration support. Contact the Student Union.com.au for details on available legal advice services for enrolled students.</t>
+          <t>Yes. The University Student Union (the Student Union) can assist with legal or migration support. Contact studentunion.example.edu for details on available legal advice services for enrolled students.</t>
         </is>
       </c>
     </row>
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>The University Student Union (the Student Union) is the student representative body offering legal and migration support, clubs and societies, events, and student advocacy. BIT students can join IT and computing clubs through the Student Union and access legal advice at the Student Union.com.au.</t>
+          <t>The University Student Union (the Student Union) is the student representative body offering legal and migration support, clubs and societies, events, and student advocacy. BIT students can join IT and computing clubs through the Student Union and access legal advice at studentunion.example.edu.</t>
         </is>
       </c>
     </row>
@@ -2818,7 +2818,7 @@
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>Yes. the University encourages students to participate in exchange programs through the University Abroad office. As a BIT student you can apply for semester-long exchanges at partner universities worldwide. Credit for courses taken abroad is assessed by the BIT program coordinator. Contact the University Abroad (uqabroad.example.edu) early - applications typically open 9–12 months before the planned exchange semester.</t>
+          <t>Yes. the University encourages students to participate in exchange programs through the University Abroad office. As a BIT student you can apply for semester-long exchanges at partner universities worldwide. Credit for courses taken abroad is assessed by the BIT program coordinator. Contact the University Abroad (studyabroad.example.edu) early - applications typically open 9–12 months before the planned exchange semester.</t>
         </is>
       </c>
     </row>
